--- a/314e-ig/output/StructureDefinition-patient-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-patient-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T16:33:40+05:30</t>
+    <t>2026-06-11T14:17:09+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -312,7 +312,7 @@
     <t>Patient.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">Meta
+    <t xml:space="preserve">Meta {http://314e.com/fhir/StructureDefinition/meta-314e}
 </t>
   </si>
   <si>
@@ -1754,7 +1754,7 @@
     <t>Patient.photo</t>
   </si>
   <si>
-    <t xml:space="preserve">Attachment
+    <t xml:space="preserve">Attachment {http://314e.com/fhir/StructureDefinition/attachment-314e}
 </t>
   </si>
   <si>

--- a/314e-ig/output/StructureDefinition-patient-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-patient-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T14:17:09+05:30</t>
+    <t>2026-06-18T13:36:33+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -609,8 +609,7 @@
   <si>
     <t>Applied at the root level of the Patient resource. Stores the patient's
 institutional or organizational affiliation (e.g., hospital network,
-physician group) using an internal code.
-Standard FHIR Patient has no affiliation field.</t>
+physician group) using an internal code.</t>
   </si>
   <si>
     <t>Patient.extension:mothersName</t>
@@ -647,7 +646,7 @@
 preferred pharmacies linked to the patient as references to Organization
 resources.
 A patient can have multiple pharmacies — each gets its own extension
-instance. Standard FHIR Patient has no pharmacy preference field.</t>
+instance.</t>
   </si>
   <si>
     <t>Patient.extension:employmentStatus</t>

--- a/314e-ig/output/StructureDefinition-patient-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-patient-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T13:36:33+05:30</t>
+    <t>2026-06-18T14:15:04+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-patient-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-patient-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T14:15:04+05:30</t>
+    <t>2026-06-18T16:14:31+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-patient-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-patient-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T16:14:31+05:30</t>
+    <t>2026-06-24T16:34:23+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2048,7 +2048,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization|Practitioner|PractitionerRole) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/organization-314e|http://314e.com/fhir/StructureDefinition/practitioner-314e|http://314e.com/fhir/StructureDefinition/practitionerrole-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -2072,7 +2072,7 @@
     <t>Patient.managingOrganization</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/organization-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -2123,7 +2123,7 @@
     <t>Patient.link.other</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-patient) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/patient-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -2481,7 +2481,7 @@
     <col min="8" max="8" width="13.1171875" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="10.75390625" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="109.55859375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="207.5" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/314e-ig/output/StructureDefinition-patient-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-patient-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T16:34:23+05:30</t>
+    <t>2026-06-29T17:18:47+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-patient-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-patient-314e.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$95</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$108</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3564" uniqueCount="678">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4041" uniqueCount="738">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T17:18:47+05:30</t>
+    <t>2026-07-01T18:18:44+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -686,6 +686,159 @@
 represented by the core FHIR elements or existing profiles.</t>
   </si>
   <si>
+    <t>Patient.extension:disability</t>
+  </si>
+  <si>
+    <t>disability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://314e.com/fhir/StructureDefinition/patient-disability-314e}
+</t>
+  </si>
+  <si>
+    <t>Physical or mental condition(s) that limit the patient's movements, senses, or activities</t>
+  </si>
+  <si>
+    <t>Value(s) identifying physical or mental condition(s) that limits a person's movements, senses, or activities. Deprecated: Use the [[[Flag]]] resource to represent disability information intended for administrative use, and to use [[[Condition]]] for clinical diagnoses that correspond to disabilities</t>
+  </si>
+  <si>
+    <t>Patient.extension:citizenship</t>
+  </si>
+  <si>
+    <t>citizenship</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://314e.com/fhir/StructureDefinition/patient-citizenship-314e}
+</t>
+  </si>
+  <si>
+    <t>The patient's legal status as citizen of a country</t>
+  </si>
+  <si>
+    <t>The patient's legal status as citizen of a country.</t>
+  </si>
+  <si>
+    <t>Patient.extension:adoptionInfo</t>
+  </si>
+  <si>
+    <t>adoptionInfo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://314e.com/fhir/StructureDefinition/patient-adoptionInfo-314e}
+</t>
+  </si>
+  <si>
+    <t>Code indicating the adoption status of the patient</t>
+  </si>
+  <si>
+    <t>Code indication the adoption status of the patient.</t>
+  </si>
+  <si>
+    <t>Patient.extension:religion</t>
+  </si>
+  <si>
+    <t>religion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://314e.com/fhir/StructureDefinition/patient-religion-314e}
+</t>
+  </si>
+  <si>
+    <t>The patient's professed religious affiliation</t>
+  </si>
+  <si>
+    <t>The patient's professed religious affiliations.</t>
+  </si>
+  <si>
+    <t>Patient.extension:importance</t>
+  </si>
+  <si>
+    <t>importance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://314e.com/fhir/StructureDefinition/patient-importance-314e}
+</t>
+  </si>
+  <si>
+    <t>The importance of the patient (e.g. VIP)</t>
+  </si>
+  <si>
+    <t>The importance of the patient (e.g. VIP). When considering using this extension you should also consider if using any or all of the following is also appropriate:
+* `Encounter.specialCourtesy` which provides a simple flag indicating additional `benefits` that the patient might be entitled to during a visit *(e.g. special room types)*.
+* `Resource.meta.security` with codes such as `VIP`. These might be used by actual data level security controls within the system, potentially requiring specific user permissions to access the data.</t>
+  </si>
+  <si>
+    <t>Patient.extension:animal</t>
+  </si>
+  <si>
+    <t>animal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://314e.com/fhir/StructureDefinition/patient-animal-314e}
+</t>
+  </si>
+  <si>
+    <t>Indicates this patient is known to be an animal</t>
+  </si>
+  <si>
+    <t>This patient is known to be an animal.</t>
+  </si>
+  <si>
+    <t>Patient.extension:individualGenderIdentity</t>
+  </si>
+  <si>
+    <t>individualGenderIdentity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://314e.com/fhir/StructureDefinition/individual-genderIdentity-314e}
+</t>
+  </si>
+  <si>
+    <t>The individual's gender identity</t>
+  </si>
+  <si>
+    <t>An individual's personal sense of being a man, woman, boy, girl, nonbinary, or something else. This represents an individual's identity, ascertained by asking them what that identity is.
+ In the case where the gender identity is communicated by a third party, for example, if a spouse indicates the gender identity of their partner on an intake form, a Provenance resource can be used with a Provenance.target referring to the Patient, with a targetElement extension identifying the gender identity extension as the target element within the Patient resource.  When exchanging this concept, refer to the guidance in the [Gender Harmony Implementation Guide](http://hl7.org/xprod/ig/uv/gender-harmony/).</t>
+  </si>
+  <si>
+    <t>Patient.extension:mothersMaidenName</t>
+  </si>
+  <si>
+    <t>mothersMaidenName</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {patient-mothersMaidenName}
+</t>
+  </si>
+  <si>
+    <t>Mother's maiden (unmarried) name</t>
+  </si>
+  <si>
+    <t>Mother's maiden (unmarried) name, commonly collected to help verify patient identity.</t>
+  </si>
+  <si>
+    <t>Role relationship to entity with maiden name (?)</t>
+  </si>
+  <si>
+    <t>PID-6</t>
+  </si>
+  <si>
+    <t>Patient.extension:cadavericDonor</t>
+  </si>
+  <si>
+    <t>cadavericDonor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {patient-cadavericDonor}
+</t>
+  </si>
+  <si>
+    <t>Flag indicating whether the patient authorized the donation of body parts after death</t>
+  </si>
+  <si>
+    <t>Flag indicating whether the patient authorized the donation of body parts after death.</t>
+  </si>
+  <si>
     <t>Patient.modifierExtension</t>
   </si>
   <si>
@@ -1361,6 +1514,46 @@
   </si>
   <si>
     <t>21112-8</t>
+  </si>
+  <si>
+    <t>Patient.birthDate.id</t>
+  </si>
+  <si>
+    <t>xml:id (or equivalent in JSON)</t>
+  </si>
+  <si>
+    <t>unique id for the element within a resource (for internal references)</t>
+  </si>
+  <si>
+    <t>Patient.birthDate.extension</t>
+  </si>
+  <si>
+    <t>Patient.birthDate.extension:birthTime</t>
+  </si>
+  <si>
+    <t>birthTime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://314e.com/fhir/StructureDefinition/patient-birthTime-314e}
+</t>
+  </si>
+  <si>
+    <t>The time of day that the patient was born</t>
+  </si>
+  <si>
+    <t>The time of day that the Patient/Person/RelatedPerson/Practitioner was born. This includes the date to ensure that the timezone information can be communicated effectively.</t>
+  </si>
+  <si>
+    <t>Patient.birthDate.value</t>
+  </si>
+  <si>
+    <t>Primitive value for date</t>
+  </si>
+  <si>
+    <t>The actual value</t>
+  </si>
+  <si>
+    <t>date.value</t>
   </si>
   <si>
     <t>Patient.deceased[x]</t>
@@ -2468,7 +2661,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO95"/>
+  <dimension ref="A1:AO108"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="36.77734375" customWidth="true" bestFit="true"/>
@@ -4979,43 +5172,41 @@
         <v>206</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="C22" s="2"/>
+        <v>132</v>
+      </c>
+      <c r="C22" t="s" s="2">
+        <v>207</v>
+      </c>
       <c r="D22" t="s" s="2">
-        <v>207</v>
+        <v>20</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="J22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>133</v>
+        <v>208</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="N22" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="O22" t="s" s="2">
-        <v>211</v>
-      </c>
+      <c r="N22" s="2"/>
+      <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>20</v>
       </c>
@@ -5063,7 +5254,7 @@
         <v>20</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>212</v>
+        <v>138</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -5078,7 +5269,7 @@
         <v>139</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>131</v>
+        <v>20</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>20</v>
@@ -5093,46 +5284,46 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="C23" s="2"/>
+        <v>132</v>
+      </c>
+      <c r="C23" t="s" s="2">
+        <v>212</v>
+      </c>
       <c r="D23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="M23" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="M23" t="s" s="2">
-        <v>216</v>
-      </c>
       <c r="N23" s="2"/>
-      <c r="O23" t="s" s="2">
-        <v>217</v>
-      </c>
+      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>20</v>
       </c>
@@ -5180,7 +5371,7 @@
         <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>213</v>
+        <v>138</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -5192,19 +5383,19 @@
         <v>20</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>218</v>
+        <v>20</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>219</v>
+        <v>20</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>220</v>
+        <v>20</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>221</v>
+        <v>20</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>20</v>
@@ -5212,12 +5403,14 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="C24" s="2"/>
+        <v>132</v>
+      </c>
+      <c r="C24" t="s" s="2">
+        <v>217</v>
+      </c>
       <c r="D24" t="s" s="2">
         <v>20</v>
       </c>
@@ -5238,13 +5431,13 @@
         <v>20</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -5295,22 +5488,22 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>226</v>
+        <v>138</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>20</v>
+        <v>139</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>227</v>
+        <v>20</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>20</v>
@@ -5327,21 +5520,23 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="C25" s="2"/>
+        <v>132</v>
+      </c>
+      <c r="C25" t="s" s="2">
+        <v>222</v>
+      </c>
       <c r="D25" t="s" s="2">
-        <v>207</v>
+        <v>20</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>20</v>
@@ -5353,17 +5548,15 @@
         <v>20</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>133</v>
+        <v>223</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>210</v>
-      </c>
+        <v>225</v>
+      </c>
+      <c r="N25" s="2"/>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>20</v>
@@ -5400,19 +5593,19 @@
         <v>20</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>136</v>
+        <v>20</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>231</v>
+        <v>20</v>
       </c>
       <c r="AD25" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>137</v>
+        <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>232</v>
+        <v>138</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -5427,7 +5620,7 @@
         <v>139</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>227</v>
+        <v>20</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>20</v>
@@ -5444,12 +5637,14 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="C26" s="2"/>
+        <v>132</v>
+      </c>
+      <c r="C26" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="D26" t="s" s="2">
         <v>20</v>
       </c>
@@ -5464,26 +5659,22 @@
         <v>20</v>
       </c>
       <c r="I26" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>108</v>
+        <v>228</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>237</v>
-      </c>
+        <v>230</v>
+      </c>
+      <c r="N26" s="2"/>
+      <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>20</v>
       </c>
@@ -5507,13 +5698,13 @@
         <v>20</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>238</v>
+        <v>20</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>239</v>
+        <v>20</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>240</v>
+        <v>20</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>20</v>
@@ -5531,22 +5722,22 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>241</v>
+        <v>138</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>242</v>
+        <v>20</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>20</v>
@@ -5555,7 +5746,7 @@
         <v>20</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>131</v>
+        <v>20</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>20</v>
@@ -5563,12 +5754,14 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="C27" s="2"/>
+        <v>132</v>
+      </c>
+      <c r="C27" t="s" s="2">
+        <v>232</v>
+      </c>
       <c r="D27" t="s" s="2">
         <v>20</v>
       </c>
@@ -5586,23 +5779,19 @@
         <v>20</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>244</v>
+        <v>233</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>245</v>
+        <v>234</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>248</v>
-      </c>
+        <v>235</v>
+      </c>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>20</v>
       </c>
@@ -5626,13 +5815,13 @@
         <v>20</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>249</v>
+        <v>20</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>250</v>
+        <v>20</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>251</v>
+        <v>20</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>20</v>
@@ -5650,22 +5839,22 @@
         <v>20</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>252</v>
+        <v>138</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>242</v>
+        <v>20</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>20</v>
@@ -5674,54 +5863,52 @@
         <v>20</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>253</v>
+        <v>20</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="C28" s="2"/>
+        <v>132</v>
+      </c>
+      <c r="C28" t="s" s="2">
+        <v>237</v>
+      </c>
       <c r="D28" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>102</v>
+        <v>238</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>255</v>
+        <v>239</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>258</v>
-      </c>
+        <v>240</v>
+      </c>
+      <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>20</v>
       </c>
@@ -5733,7 +5920,7 @@
         <v>20</v>
       </c>
       <c r="T28" t="s" s="2">
-        <v>259</v>
+        <v>20</v>
       </c>
       <c r="U28" t="s" s="2">
         <v>20</v>
@@ -5769,22 +5956,22 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>260</v>
+        <v>138</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>261</v>
+        <v>20</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>20</v>
@@ -5793,51 +5980,51 @@
         <v>20</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>262</v>
+        <v>20</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>263</v>
+        <v>241</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="C29" s="2"/>
+        <v>132</v>
+      </c>
+      <c r="C29" t="s" s="2">
+        <v>242</v>
+      </c>
       <c r="D29" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>223</v>
+        <v>243</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>264</v>
+        <v>244</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>266</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>20</v>
@@ -5850,7 +6037,7 @@
         <v>20</v>
       </c>
       <c r="T29" t="s" s="2">
-        <v>267</v>
+        <v>20</v>
       </c>
       <c r="U29" t="s" s="2">
         <v>20</v>
@@ -5886,22 +6073,22 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>268</v>
+        <v>138</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>269</v>
+        <v>246</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>20</v>
@@ -5910,7 +6097,7 @@
         <v>20</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>270</v>
+        <v>247</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>20</v>
@@ -5918,12 +6105,14 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>271</v>
+        <v>248</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="C30" s="2"/>
+        <v>132</v>
+      </c>
+      <c r="C30" t="s" s="2">
+        <v>249</v>
+      </c>
       <c r="D30" t="s" s="2">
         <v>20</v>
       </c>
@@ -5941,16 +6130,16 @@
         <v>20</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>272</v>
+        <v>250</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>273</v>
+        <v>251</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>274</v>
+        <v>252</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -6001,22 +6190,22 @@
         <v>20</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>275</v>
+        <v>138</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>276</v>
+        <v>20</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>20</v>
@@ -6025,7 +6214,7 @@
         <v>20</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>277</v>
+        <v>20</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>20</v>
@@ -6033,44 +6222,46 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>278</v>
+        <v>253</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>278</v>
+        <v>253</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>20</v>
+        <v>254</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>279</v>
+        <v>133</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>280</v>
+        <v>255</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>281</v>
+        <v>256</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="O31" s="2"/>
+        <v>257</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>258</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>20</v>
       </c>
@@ -6118,22 +6309,22 @@
         <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>283</v>
+        <v>259</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>284</v>
+        <v>131</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>20</v>
@@ -6142,18 +6333,18 @@
         <v>20</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>285</v>
+        <v>20</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="32" hidden="true">
+    <row r="32">
       <c r="A32" t="s" s="2">
-        <v>286</v>
+        <v>260</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>286</v>
+        <v>260</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6161,41 +6352,37 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="J32" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>287</v>
+        <v>261</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>288</v>
+        <v>262</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>290</v>
-      </c>
+        <v>263</v>
+      </c>
+      <c r="N32" s="2"/>
       <c r="O32" t="s" s="2">
-        <v>291</v>
+        <v>264</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>20</v>
       </c>
-      <c r="Q32" t="s" s="2">
-        <v>292</v>
-      </c>
+      <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
         <v>20</v>
       </c>
@@ -6239,13 +6426,13 @@
         <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>286</v>
+        <v>260</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>20</v>
@@ -6254,27 +6441,27 @@
         <v>100</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>293</v>
+        <v>265</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>227</v>
+        <v>266</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>294</v>
+        <v>267</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>20</v>
+        <v>268</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>295</v>
+        <v>269</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>295</v>
+        <v>269</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6282,35 +6469,31 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G33" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="G33" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="H33" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>296</v>
+        <v>270</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>297</v>
+        <v>271</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>300</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="N33" s="2"/>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>20</v>
       </c>
@@ -6358,31 +6541,31 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>295</v>
+        <v>273</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>301</v>
+        <v>20</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>302</v>
+        <v>274</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>303</v>
+        <v>20</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>304</v>
+        <v>20</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>20</v>
@@ -6390,21 +6573,21 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>305</v>
+        <v>275</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>305</v>
+        <v>275</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>20</v>
+        <v>254</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>20</v>
@@ -6416,15 +6599,17 @@
         <v>20</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>223</v>
+        <v>133</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>224</v>
+        <v>276</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="N34" s="2"/>
+        <v>277</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>257</v>
+      </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>20</v>
@@ -6461,34 +6646,34 @@
         <v>20</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>20</v>
+        <v>136</v>
       </c>
       <c r="AC34" t="s" s="2">
-        <v>20</v>
+        <v>278</v>
       </c>
       <c r="AD34" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>20</v>
+        <v>137</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>226</v>
+        <v>279</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>20</v>
+        <v>139</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>227</v>
+        <v>274</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>20</v>
@@ -6505,44 +6690,46 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>306</v>
+        <v>280</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>306</v>
+        <v>280</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>207</v>
+        <v>20</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>133</v>
+        <v>108</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>229</v>
+        <v>281</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>230</v>
+        <v>282</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="O35" s="2"/>
+        <v>283</v>
+      </c>
+      <c r="O35" t="s" s="2">
+        <v>284</v>
+      </c>
       <c r="P35" t="s" s="2">
         <v>20</v>
       </c>
@@ -6566,46 +6753,46 @@
         <v>20</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>20</v>
+        <v>285</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>20</v>
+        <v>286</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>20</v>
+        <v>287</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>136</v>
+        <v>20</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>231</v>
+        <v>20</v>
       </c>
       <c r="AD35" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>137</v>
+        <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>232</v>
+        <v>288</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>227</v>
+        <v>289</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>20</v>
@@ -6614,7 +6801,7 @@
         <v>20</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>20</v>
+        <v>131</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>20</v>
@@ -6622,10 +6809,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>307</v>
+        <v>290</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>307</v>
+        <v>290</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6642,25 +6829,25 @@
         <v>20</v>
       </c>
       <c r="I36" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="J36" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>108</v>
+        <v>291</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>308</v>
+        <v>292</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>309</v>
+        <v>293</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>310</v>
+        <v>294</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>311</v>
+        <v>295</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>20</v>
@@ -6685,13 +6872,13 @@
         <v>20</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>238</v>
+        <v>296</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>312</v>
+        <v>297</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>313</v>
+        <v>298</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>20</v>
@@ -6709,7 +6896,7 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>314</v>
+        <v>299</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -6724,7 +6911,7 @@
         <v>100</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>315</v>
+        <v>289</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>20</v>
@@ -6733,18 +6920,18 @@
         <v>20</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>316</v>
+        <v>300</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="37" hidden="true">
+    <row r="37">
       <c r="A37" t="s" s="2">
-        <v>317</v>
+        <v>301</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>317</v>
+        <v>301</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6752,13 +6939,13 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>20</v>
@@ -6767,19 +6954,19 @@
         <v>89</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>223</v>
+        <v>102</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>318</v>
+        <v>302</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>319</v>
+        <v>303</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>321</v>
+        <v>305</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>20</v>
@@ -6792,7 +6979,7 @@
         <v>20</v>
       </c>
       <c r="T37" t="s" s="2">
-        <v>20</v>
+        <v>306</v>
       </c>
       <c r="U37" t="s" s="2">
         <v>20</v>
@@ -6828,7 +7015,7 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>322</v>
+        <v>307</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -6843,7 +7030,7 @@
         <v>100</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>323</v>
+        <v>308</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>20</v>
@@ -6852,7 +7039,7 @@
         <v>20</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>324</v>
+        <v>309</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>20</v>
@@ -6860,18 +7047,18 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>325</v>
+        <v>310</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>325</v>
+        <v>310</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>326</v>
+        <v>20</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>88</v>
@@ -6886,16 +7073,16 @@
         <v>89</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>223</v>
+        <v>270</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>327</v>
+        <v>311</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>328</v>
+        <v>312</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>329</v>
+        <v>313</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6909,7 +7096,7 @@
         <v>20</v>
       </c>
       <c r="T38" t="s" s="2">
-        <v>20</v>
+        <v>314</v>
       </c>
       <c r="U38" t="s" s="2">
         <v>20</v>
@@ -6945,7 +7132,7 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>330</v>
+        <v>315</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -6954,13 +7141,13 @@
         <v>88</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>331</v>
+        <v>20</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>332</v>
+        <v>316</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>20</v>
@@ -6969,32 +7156,32 @@
         <v>20</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>333</v>
+        <v>317</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>334</v>
+        <v>318</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>334</v>
+        <v>318</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>335</v>
+        <v>20</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>20</v>
@@ -7003,17 +7190,15 @@
         <v>89</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>223</v>
+        <v>319</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>336</v>
+        <v>320</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>338</v>
-      </c>
+        <v>321</v>
+      </c>
+      <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>20</v>
@@ -7062,22 +7247,22 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>339</v>
+        <v>322</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>331</v>
+        <v>20</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>340</v>
+        <v>323</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>20</v>
@@ -7086,7 +7271,7 @@
         <v>20</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>341</v>
+        <v>324</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>20</v>
@@ -7094,10 +7279,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>342</v>
+        <v>325</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>342</v>
+        <v>325</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7108,7 +7293,7 @@
         <v>79</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>20</v>
@@ -7120,15 +7305,17 @@
         <v>89</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>223</v>
+        <v>326</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>343</v>
+        <v>327</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="N40" s="2"/>
+        <v>328</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>329</v>
+      </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>20</v>
@@ -7177,13 +7364,13 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>345</v>
+        <v>330</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>20</v>
@@ -7192,7 +7379,7 @@
         <v>100</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>346</v>
+        <v>331</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>20</v>
@@ -7201,7 +7388,7 @@
         <v>20</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>347</v>
+        <v>332</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>20</v>
@@ -7209,10 +7396,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>348</v>
+        <v>333</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>348</v>
+        <v>333</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7223,32 +7410,38 @@
         <v>79</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I41" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="J41" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>223</v>
+        <v>334</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>349</v>
+        <v>335</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="N41" s="2"/>
-      <c r="O41" s="2"/>
+        <v>336</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>338</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>20</v>
       </c>
-      <c r="Q41" s="2"/>
+      <c r="Q41" t="s" s="2">
+        <v>339</v>
+      </c>
       <c r="R41" t="s" s="2">
         <v>20</v>
       </c>
@@ -7292,13 +7485,13 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>351</v>
+        <v>333</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>20</v>
@@ -7307,27 +7500,27 @@
         <v>100</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>352</v>
+        <v>340</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>20</v>
+        <v>274</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>20</v>
+        <v>341</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>353</v>
+        <v>20</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="42" hidden="true">
+    <row r="42">
       <c r="A42" t="s" s="2">
-        <v>354</v>
+        <v>342</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>354</v>
+        <v>342</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7335,13 +7528,13 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>20</v>
@@ -7350,17 +7543,19 @@
         <v>89</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>272</v>
+        <v>343</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>355</v>
+        <v>344</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="N42" s="2"/>
+        <v>345</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>346</v>
+      </c>
       <c r="O42" t="s" s="2">
-        <v>357</v>
+        <v>347</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>20</v>
@@ -7409,31 +7604,31 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>358</v>
+        <v>342</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>100</v>
+        <v>348</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>20</v>
+        <v>350</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>20</v>
@@ -7441,10 +7636,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7455,7 +7650,7 @@
         <v>79</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>20</v>
@@ -7464,23 +7659,19 @@
         <v>20</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>362</v>
+        <v>270</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>363</v>
+        <v>271</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>366</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="N43" s="2"/>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>20</v>
       </c>
@@ -7528,31 +7719,31 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>361</v>
+        <v>273</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>367</v>
+        <v>274</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>368</v>
+        <v>20</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>369</v>
+        <v>20</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>20</v>
@@ -7560,21 +7751,21 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>370</v>
+        <v>353</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>370</v>
+        <v>353</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>20</v>
+        <v>254</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>20</v>
@@ -7586,15 +7777,17 @@
         <v>20</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>223</v>
+        <v>133</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>224</v>
+        <v>276</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="N44" s="2"/>
+        <v>277</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>257</v>
+      </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>20</v>
@@ -7631,34 +7824,34 @@
         <v>20</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>20</v>
+        <v>136</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>20</v>
+        <v>278</v>
       </c>
       <c r="AD44" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>20</v>
+        <v>137</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>226</v>
+        <v>279</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>20</v>
+        <v>139</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>227</v>
+        <v>274</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>20</v>
@@ -7675,44 +7868,46 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>371</v>
+        <v>354</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>371</v>
+        <v>354</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>207</v>
+        <v>20</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>133</v>
+        <v>108</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>229</v>
+        <v>355</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>230</v>
+        <v>356</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="O45" s="2"/>
+        <v>357</v>
+      </c>
+      <c r="O45" t="s" s="2">
+        <v>358</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>20</v>
       </c>
@@ -7736,46 +7931,46 @@
         <v>20</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>20</v>
+        <v>285</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>20</v>
+        <v>359</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>20</v>
+        <v>360</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>136</v>
+        <v>20</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>231</v>
+        <v>20</v>
       </c>
       <c r="AD45" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>137</v>
+        <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>232</v>
+        <v>361</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>227</v>
+        <v>362</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>20</v>
@@ -7784,18 +7979,18 @@
         <v>20</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>20</v>
+        <v>363</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7803,13 +7998,13 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G46" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>20</v>
@@ -7818,16 +8013,20 @@
         <v>89</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>108</v>
+        <v>270</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="N46" s="2"/>
-      <c r="O46" s="2"/>
+        <v>366</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="O46" t="s" s="2">
+        <v>368</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>20</v>
       </c>
@@ -7851,13 +8050,13 @@
         <v>20</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>238</v>
+        <v>20</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>375</v>
+        <v>20</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>376</v>
+        <v>20</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>20</v>
@@ -7875,7 +8074,7 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>377</v>
+        <v>369</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -7884,13 +8083,13 @@
         <v>88</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>378</v>
+        <v>20</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>379</v>
+        <v>370</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>20</v>
@@ -7899,7 +8098,7 @@
         <v>20</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>20</v>
@@ -7907,18 +8106,18 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>20</v>
+        <v>373</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G47" t="s" s="2">
         <v>88</v>
@@ -7933,20 +8132,18 @@
         <v>89</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>223</v>
+        <v>270</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>382</v>
+        <v>374</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>383</v>
+        <v>375</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>385</v>
-      </c>
+        <v>376</v>
+      </c>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>20</v>
       </c>
@@ -7994,7 +8191,7 @@
         <v>20</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -8003,13 +8200,13 @@
         <v>88</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>20</v>
+        <v>378</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>387</v>
+        <v>379</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>20</v>
@@ -8018,7 +8215,7 @@
         <v>20</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>388</v>
+        <v>380</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>20</v>
@@ -8026,46 +8223,44 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>389</v>
+        <v>381</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>389</v>
+        <v>381</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>20</v>
+        <v>382</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>89</v>
       </c>
       <c r="I48" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="J48" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>108</v>
+        <v>270</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>393</v>
-      </c>
+        <v>385</v>
+      </c>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>20</v>
       </c>
@@ -8089,11 +8284,13 @@
         <v>20</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="Y48" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="Y48" t="s" s="2">
+        <v>20</v>
+      </c>
       <c r="Z48" t="s" s="2">
-        <v>394</v>
+        <v>20</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>20</v>
@@ -8111,22 +8308,22 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>395</v>
+        <v>386</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>20</v>
+        <v>378</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>315</v>
+        <v>387</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>20</v>
@@ -8135,7 +8332,7 @@
         <v>20</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>20</v>
@@ -8143,10 +8340,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8157,7 +8354,7 @@
         <v>79</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>20</v>
@@ -8169,17 +8366,15 @@
         <v>89</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>398</v>
+        <v>270</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>399</v>
+        <v>390</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>401</v>
-      </c>
+        <v>391</v>
+      </c>
+      <c r="N49" s="2"/>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>20</v>
@@ -8228,13 +8423,13 @@
         <v>20</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>402</v>
+        <v>392</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>20</v>
@@ -8243,7 +8438,7 @@
         <v>100</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>227</v>
+        <v>393</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>20</v>
@@ -8252,7 +8447,7 @@
         <v>20</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>227</v>
+        <v>394</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>20</v>
@@ -8260,10 +8455,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>403</v>
+        <v>395</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>403</v>
+        <v>395</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8274,7 +8469,7 @@
         <v>79</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>20</v>
@@ -8286,13 +8481,13 @@
         <v>89</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -8343,13 +8538,13 @@
         <v>20</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>20</v>
@@ -8358,7 +8553,7 @@
         <v>100</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>359</v>
+        <v>399</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>20</v>
@@ -8367,18 +8562,18 @@
         <v>20</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>131</v>
+        <v>400</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8386,13 +8581,13 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G51" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>20</v>
@@ -8401,19 +8596,17 @@
         <v>89</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>108</v>
+        <v>319</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>410</v>
-      </c>
+        <v>403</v>
+      </c>
+      <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>20</v>
@@ -8438,11 +8631,13 @@
         <v>20</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="Y51" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="Y51" t="s" s="2">
+        <v>20</v>
+      </c>
       <c r="Z51" t="s" s="2">
-        <v>412</v>
+        <v>20</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>20</v>
@@ -8460,7 +8655,7 @@
         <v>20</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -8475,27 +8670,27 @@
         <v>100</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>164</v>
+        <v>406</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>413</v>
+        <v>20</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>415</v>
+        <v>408</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>415</v>
+        <v>408</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8506,10 +8701,10 @@
         <v>79</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>20</v>
@@ -8518,19 +8713,19 @@
         <v>89</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>416</v>
+        <v>409</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>417</v>
+        <v>410</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>418</v>
+        <v>411</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>419</v>
+        <v>412</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>20</v>
@@ -8579,13 +8774,13 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>415</v>
+        <v>408</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>20</v>
@@ -8594,27 +8789,27 @@
         <v>100</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>422</v>
+        <v>415</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>423</v>
+        <v>416</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>424</v>
+        <v>20</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>425</v>
+        <v>417</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>425</v>
+        <v>417</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8631,26 +8826,22 @@
         <v>20</v>
       </c>
       <c r="I53" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>426</v>
+        <v>270</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>427</v>
+        <v>271</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>430</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="N53" s="2"/>
+      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>20</v>
       </c>
@@ -8698,7 +8889,7 @@
         <v>20</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>425</v>
+        <v>273</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -8710,34 +8901,34 @@
         <v>20</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>431</v>
+        <v>274</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>227</v>
+        <v>20</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>432</v>
+        <v>20</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>433</v>
+        <v>418</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>433</v>
+        <v>418</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>20</v>
+        <v>254</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8747,29 +8938,27 @@
         <v>80</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>434</v>
+        <v>133</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>435</v>
+        <v>276</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>436</v>
+        <v>277</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>438</v>
-      </c>
+        <v>257</v>
+      </c>
+      <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>20</v>
       </c>
@@ -8805,19 +8994,19 @@
         <v>20</v>
       </c>
       <c r="AB54" t="s" s="2">
-        <v>20</v>
+        <v>136</v>
       </c>
       <c r="AC54" t="s" s="2">
-        <v>20</v>
+        <v>278</v>
       </c>
       <c r="AD54" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>20</v>
+        <v>137</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>433</v>
+        <v>279</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8829,30 +9018,30 @@
         <v>20</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>439</v>
+        <v>274</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>440</v>
+        <v>20</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>441</v>
+        <v>20</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="55" hidden="true">
+    <row r="55">
       <c r="A55" t="s" s="2">
-        <v>442</v>
+        <v>419</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>442</v>
+        <v>419</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8860,28 +9049,28 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G55" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>223</v>
+        <v>108</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>224</v>
+        <v>420</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>225</v>
+        <v>421</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8908,13 +9097,13 @@
         <v>20</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>20</v>
+        <v>285</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>20</v>
+        <v>422</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>20</v>
+        <v>423</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>20</v>
@@ -8932,7 +9121,7 @@
         <v>20</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>226</v>
+        <v>424</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8941,13 +9130,13 @@
         <v>88</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>20</v>
+        <v>425</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>227</v>
+        <v>426</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>20</v>
@@ -8956,52 +9145,54 @@
         <v>20</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>20</v>
+        <v>427</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="56" hidden="true">
+    <row r="56">
       <c r="A56" t="s" s="2">
-        <v>443</v>
+        <v>428</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>443</v>
+        <v>428</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>207</v>
+        <v>20</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>133</v>
+        <v>270</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>229</v>
+        <v>429</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>230</v>
+        <v>430</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="O56" s="2"/>
+        <v>431</v>
+      </c>
+      <c r="O56" t="s" s="2">
+        <v>432</v>
+      </c>
       <c r="P56" t="s" s="2">
         <v>20</v>
       </c>
@@ -9037,34 +9228,34 @@
         <v>20</v>
       </c>
       <c r="AB56" t="s" s="2">
-        <v>136</v>
+        <v>20</v>
       </c>
       <c r="AC56" t="s" s="2">
-        <v>231</v>
+        <v>20</v>
       </c>
       <c r="AD56" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE56" t="s" s="2">
-        <v>137</v>
+        <v>20</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>232</v>
+        <v>433</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>227</v>
+        <v>434</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>20</v>
@@ -9073,22 +9264,20 @@
         <v>20</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>20</v>
+        <v>435</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="57" hidden="true">
+    <row r="57">
       <c r="A57" t="s" s="2">
-        <v>444</v>
+        <v>436</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="C57" t="s" s="2">
-        <v>445</v>
-      </c>
+        <v>436</v>
+      </c>
+      <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
         <v>20</v>
       </c>
@@ -9100,27 +9289,29 @@
         <v>88</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="I57" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>446</v>
+        <v>108</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>447</v>
+        <v>437</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>448</v>
+        <v>438</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="O57" s="2"/>
+        <v>439</v>
+      </c>
+      <c r="O57" t="s" s="2">
+        <v>440</v>
+      </c>
       <c r="P57" t="s" s="2">
         <v>20</v>
       </c>
@@ -9144,13 +9335,11 @@
         <v>20</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y57" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>285</v>
+      </c>
+      <c r="Y57" s="2"/>
       <c r="Z57" t="s" s="2">
-        <v>20</v>
+        <v>441</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>20</v>
@@ -9168,22 +9357,22 @@
         <v>20</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>232</v>
+        <v>442</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>20</v>
+        <v>362</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>20</v>
@@ -9192,7 +9381,7 @@
         <v>20</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>20</v>
+        <v>443</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>20</v>
@@ -9200,10 +9389,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9220,26 +9409,24 @@
         <v>20</v>
       </c>
       <c r="I58" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="J58" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>108</v>
+        <v>445</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>454</v>
-      </c>
+        <v>448</v>
+      </c>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>20</v>
       </c>
@@ -9251,7 +9438,7 @@
         <v>20</v>
       </c>
       <c r="T58" t="s" s="2">
-        <v>455</v>
+        <v>20</v>
       </c>
       <c r="U58" t="s" s="2">
         <v>20</v>
@@ -9263,13 +9450,13 @@
         <v>20</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>238</v>
+        <v>20</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>456</v>
+        <v>20</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>457</v>
+        <v>20</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>20</v>
@@ -9287,7 +9474,7 @@
         <v>20</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>458</v>
+        <v>449</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -9302,7 +9489,7 @@
         <v>100</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>315</v>
+        <v>274</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>20</v>
@@ -9311,7 +9498,7 @@
         <v>20</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>459</v>
+        <v>274</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>20</v>
@@ -9319,10 +9506,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>460</v>
+        <v>450</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>460</v>
+        <v>450</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9345,17 +9532,15 @@
         <v>89</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>108</v>
+        <v>319</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>461</v>
+        <v>451</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>463</v>
-      </c>
+        <v>452</v>
+      </c>
+      <c r="N59" s="2"/>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>20</v>
@@ -9368,7 +9553,7 @@
         <v>20</v>
       </c>
       <c r="T59" t="s" s="2">
-        <v>464</v>
+        <v>20</v>
       </c>
       <c r="U59" t="s" s="2">
         <v>20</v>
@@ -9380,13 +9565,13 @@
         <v>20</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>238</v>
+        <v>20</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>465</v>
+        <v>20</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>466</v>
+        <v>20</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>20</v>
@@ -9404,7 +9589,7 @@
         <v>20</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>467</v>
+        <v>453</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -9419,7 +9604,7 @@
         <v>100</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>315</v>
+        <v>406</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>20</v>
@@ -9428,18 +9613,18 @@
         <v>20</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>468</v>
+        <v>131</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="60" hidden="true">
+    <row r="60">
       <c r="A60" t="s" s="2">
-        <v>469</v>
+        <v>454</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>469</v>
+        <v>454</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9447,13 +9632,13 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G60" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>20</v>
@@ -9462,19 +9647,19 @@
         <v>89</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>223</v>
+        <v>108</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>470</v>
+        <v>455</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>471</v>
+        <v>456</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>472</v>
+        <v>457</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>321</v>
+        <v>458</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>20</v>
@@ -9487,7 +9672,7 @@
         <v>20</v>
       </c>
       <c r="T60" t="s" s="2">
-        <v>473</v>
+        <v>20</v>
       </c>
       <c r="U60" t="s" s="2">
         <v>20</v>
@@ -9499,13 +9684,11 @@
         <v>20</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y60" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>285</v>
+      </c>
+      <c r="Y60" s="2"/>
       <c r="Z60" t="s" s="2">
-        <v>20</v>
+        <v>459</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>20</v>
@@ -9523,7 +9706,7 @@
         <v>20</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>474</v>
+        <v>454</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -9538,16 +9721,16 @@
         <v>100</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>323</v>
+        <v>164</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>20</v>
+        <v>460</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>475</v>
+        <v>461</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>20</v>
@@ -9555,10 +9738,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>476</v>
+        <v>462</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>476</v>
+        <v>462</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9569,7 +9752,7 @@
         <v>79</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>89</v>
@@ -9581,16 +9764,20 @@
         <v>89</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>223</v>
+        <v>463</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>477</v>
+        <v>464</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="N61" s="2"/>
-      <c r="O61" s="2"/>
+        <v>465</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="O61" t="s" s="2">
+        <v>467</v>
+      </c>
       <c r="P61" t="s" s="2">
         <v>20</v>
       </c>
@@ -9602,7 +9789,7 @@
         <v>20</v>
       </c>
       <c r="T61" t="s" s="2">
-        <v>479</v>
+        <v>20</v>
       </c>
       <c r="U61" t="s" s="2">
         <v>20</v>
@@ -9638,13 +9825,13 @@
         <v>20</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>480</v>
+        <v>462</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>20</v>
@@ -9653,31 +9840,31 @@
         <v>100</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>481</v>
+        <v>468</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>20</v>
+        <v>469</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>482</v>
+        <v>470</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>20</v>
+        <v>471</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>484</v>
+        <v>20</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -9687,22 +9874,22 @@
         <v>88</v>
       </c>
       <c r="H62" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="I62" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>223</v>
+        <v>270</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>485</v>
+        <v>473</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>486</v>
+        <v>474</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9717,7 +9904,7 @@
         <v>20</v>
       </c>
       <c r="T62" t="s" s="2">
-        <v>487</v>
+        <v>20</v>
       </c>
       <c r="U62" t="s" s="2">
         <v>20</v>
@@ -9753,7 +9940,7 @@
         <v>20</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>488</v>
+        <v>273</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -9765,10 +9952,10 @@
         <v>20</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>489</v>
+        <v>20</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>20</v>
@@ -9777,7 +9964,7 @@
         <v>20</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>490</v>
+        <v>20</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>20</v>
@@ -9785,21 +9972,21 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>491</v>
+        <v>475</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>491</v>
+        <v>475</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>492</v>
+        <v>20</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>20</v>
@@ -9808,20 +9995,18 @@
         <v>20</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>223</v>
+        <v>133</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>493</v>
+        <v>134</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>495</v>
-      </c>
+        <v>135</v>
+      </c>
+      <c r="N63" s="2"/>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>20</v>
@@ -9834,7 +10019,7 @@
         <v>20</v>
       </c>
       <c r="T63" t="s" s="2">
-        <v>496</v>
+        <v>20</v>
       </c>
       <c r="U63" t="s" s="2">
         <v>20</v>
@@ -9858,34 +10043,32 @@
         <v>20</v>
       </c>
       <c r="AB63" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC63" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="AC63" s="2"/>
       <c r="AD63" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>20</v>
+        <v>137</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>497</v>
+        <v>279</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>498</v>
+        <v>20</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>20</v>
@@ -9894,22 +10077,24 @@
         <v>20</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>499</v>
+        <v>20</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>500</v>
+        <v>476</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="C64" s="2"/>
+        <v>475</v>
+      </c>
+      <c r="C64" t="s" s="2">
+        <v>477</v>
+      </c>
       <c r="D64" t="s" s="2">
-        <v>501</v>
+        <v>20</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -9919,22 +10104,22 @@
         <v>88</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>223</v>
+        <v>478</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>502</v>
+        <v>479</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>503</v>
+        <v>480</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9949,7 +10134,7 @@
         <v>20</v>
       </c>
       <c r="T64" t="s" s="2">
-        <v>504</v>
+        <v>20</v>
       </c>
       <c r="U64" t="s" s="2">
         <v>20</v>
@@ -9961,13 +10146,13 @@
         <v>20</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>249</v>
+        <v>20</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>505</v>
+        <v>20</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>506</v>
+        <v>20</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>20</v>
@@ -9985,22 +10170,22 @@
         <v>20</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>507</v>
+        <v>279</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>20</v>
+        <v>152</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>508</v>
+        <v>20</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>20</v>
@@ -10009,22 +10194,22 @@
         <v>20</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>509</v>
+        <v>20</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>510</v>
+        <v>481</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>510</v>
+        <v>481</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>511</v>
+        <v>20</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -10034,22 +10219,22 @@
         <v>88</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>223</v>
+        <v>463</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>512</v>
+        <v>482</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>513</v>
+        <v>483</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -10064,7 +10249,7 @@
         <v>20</v>
       </c>
       <c r="T65" t="s" s="2">
-        <v>514</v>
+        <v>20</v>
       </c>
       <c r="U65" t="s" s="2">
         <v>20</v>
@@ -10100,7 +10285,7 @@
         <v>20</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>515</v>
+        <v>484</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -10112,10 +10297,10 @@
         <v>20</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>516</v>
+        <v>20</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>20</v>
@@ -10124,7 +10309,7 @@
         <v>20</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>517</v>
+        <v>20</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>20</v>
@@ -10132,10 +10317,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>518</v>
+        <v>485</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>518</v>
+        <v>485</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10152,24 +10337,26 @@
         <v>20</v>
       </c>
       <c r="I66" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="J66" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>223</v>
+        <v>486</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>519</v>
+        <v>487</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>520</v>
+        <v>488</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="O66" s="2"/>
+        <v>489</v>
+      </c>
+      <c r="O66" t="s" s="2">
+        <v>490</v>
+      </c>
       <c r="P66" t="s" s="2">
         <v>20</v>
       </c>
@@ -10217,7 +10404,7 @@
         <v>20</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>522</v>
+        <v>485</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -10232,27 +10419,27 @@
         <v>100</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>523</v>
+        <v>491</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>20</v>
+        <v>274</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>524</v>
+        <v>492</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="67" hidden="true">
+    <row r="67">
       <c r="A67" t="s" s="2">
-        <v>525</v>
+        <v>493</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>525</v>
+        <v>493</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10263,10 +10450,10 @@
         <v>79</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H67" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="I67" t="s" s="2">
         <v>20</v>
@@ -10275,17 +10462,19 @@
         <v>89</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>272</v>
+        <v>494</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>526</v>
+        <v>495</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="N67" s="2"/>
+        <v>496</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>497</v>
+      </c>
       <c r="O67" t="s" s="2">
-        <v>528</v>
+        <v>498</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>20</v>
@@ -10298,7 +10487,7 @@
         <v>20</v>
       </c>
       <c r="T67" t="s" s="2">
-        <v>529</v>
+        <v>20</v>
       </c>
       <c r="U67" t="s" s="2">
         <v>20</v>
@@ -10334,13 +10523,13 @@
         <v>20</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>530</v>
+        <v>493</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>20</v>
@@ -10349,16 +10538,16 @@
         <v>100</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>359</v>
+        <v>499</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>20</v>
+        <v>500</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>531</v>
+        <v>501</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>20</v>
@@ -10366,10 +10555,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>532</v>
+        <v>502</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>532</v>
+        <v>502</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10392,18 +10581,16 @@
         <v>20</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>533</v>
+        <v>270</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>534</v>
+        <v>271</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>535</v>
+        <v>272</v>
       </c>
       <c r="N68" s="2"/>
-      <c r="O68" t="s" s="2">
-        <v>536</v>
-      </c>
+      <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>20</v>
       </c>
@@ -10427,13 +10614,13 @@
         <v>20</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>249</v>
+        <v>20</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>537</v>
+        <v>20</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>538</v>
+        <v>20</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>20</v>
@@ -10451,7 +10638,7 @@
         <v>20</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>532</v>
+        <v>273</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -10463,19 +10650,19 @@
         <v>20</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>539</v>
+        <v>274</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>540</v>
+        <v>20</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>541</v>
+        <v>20</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>20</v>
@@ -10483,21 +10670,21 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>542</v>
+        <v>503</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>542</v>
+        <v>503</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>20</v>
+        <v>254</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>20</v>
@@ -10509,20 +10696,18 @@
         <v>20</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>543</v>
+        <v>133</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>544</v>
+        <v>276</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>545</v>
+        <v>277</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>546</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>547</v>
-      </c>
+        <v>257</v>
+      </c>
+      <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>20</v>
       </c>
@@ -10558,43 +10743,43 @@
         <v>20</v>
       </c>
       <c r="AB69" t="s" s="2">
-        <v>20</v>
+        <v>136</v>
       </c>
       <c r="AC69" t="s" s="2">
-        <v>20</v>
+        <v>278</v>
       </c>
       <c r="AD69" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE69" t="s" s="2">
-        <v>20</v>
+        <v>137</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>542</v>
+        <v>279</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>548</v>
+        <v>274</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>227</v>
+        <v>20</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>549</v>
+        <v>20</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>20</v>
@@ -10602,12 +10787,14 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>550</v>
+        <v>504</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="C70" s="2"/>
+        <v>503</v>
+      </c>
+      <c r="C70" t="s" s="2">
+        <v>505</v>
+      </c>
       <c r="D70" t="s" s="2">
         <v>20</v>
       </c>
@@ -10616,7 +10803,7 @@
         <v>79</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>20</v>
@@ -10628,20 +10815,18 @@
         <v>20</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>551</v>
+        <v>506</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>552</v>
+        <v>507</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>553</v>
+        <v>508</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>554</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>555</v>
-      </c>
+        <v>509</v>
+      </c>
+      <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>20</v>
       </c>
@@ -10689,7 +10874,7 @@
         <v>20</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>550</v>
+        <v>279</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -10701,19 +10886,19 @@
         <v>20</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>556</v>
+        <v>20</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>227</v>
+        <v>20</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>557</v>
+        <v>20</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>20</v>
@@ -10721,10 +10906,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>558</v>
+        <v>510</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>558</v>
+        <v>510</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10735,31 +10920,31 @@
         <v>79</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I71" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>559</v>
+        <v>108</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>560</v>
+        <v>511</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>561</v>
+        <v>512</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>562</v>
+        <v>513</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>563</v>
+        <v>514</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>20</v>
@@ -10772,7 +10957,7 @@
         <v>20</v>
       </c>
       <c r="T71" t="s" s="2">
-        <v>20</v>
+        <v>515</v>
       </c>
       <c r="U71" t="s" s="2">
         <v>20</v>
@@ -10784,13 +10969,13 @@
         <v>20</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>20</v>
+        <v>285</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>20</v>
+        <v>516</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>20</v>
+        <v>517</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>20</v>
@@ -10808,31 +10993,31 @@
         <v>20</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>558</v>
+        <v>518</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>564</v>
+        <v>100</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>565</v>
+        <v>362</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>227</v>
+        <v>20</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>20</v>
+        <v>519</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>20</v>
@@ -10840,10 +11025,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>566</v>
+        <v>520</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>566</v>
+        <v>520</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10863,18 +11048,20 @@
         <v>20</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>223</v>
+        <v>108</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>224</v>
+        <v>521</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="N72" s="2"/>
+        <v>522</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>523</v>
+      </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>20</v>
@@ -10887,7 +11074,7 @@
         <v>20</v>
       </c>
       <c r="T72" t="s" s="2">
-        <v>20</v>
+        <v>524</v>
       </c>
       <c r="U72" t="s" s="2">
         <v>20</v>
@@ -10899,13 +11086,13 @@
         <v>20</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>20</v>
+        <v>285</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>20</v>
+        <v>525</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>20</v>
+        <v>526</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>20</v>
@@ -10923,7 +11110,7 @@
         <v>20</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>226</v>
+        <v>527</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10935,10 +11122,10 @@
         <v>20</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>227</v>
+        <v>362</v>
       </c>
       <c r="AL72" t="s" s="2">
         <v>20</v>
@@ -10947,7 +11134,7 @@
         <v>20</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>20</v>
+        <v>528</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>20</v>
@@ -10955,21 +11142,21 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>567</v>
+        <v>529</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>567</v>
+        <v>529</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>207</v>
+        <v>20</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>20</v>
@@ -10978,21 +11165,23 @@
         <v>20</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>133</v>
+        <v>270</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>229</v>
+        <v>530</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>230</v>
+        <v>531</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="O73" s="2"/>
+        <v>532</v>
+      </c>
+      <c r="O73" t="s" s="2">
+        <v>368</v>
+      </c>
       <c r="P73" t="s" s="2">
         <v>20</v>
       </c>
@@ -11004,7 +11193,7 @@
         <v>20</v>
       </c>
       <c r="T73" t="s" s="2">
-        <v>20</v>
+        <v>533</v>
       </c>
       <c r="U73" t="s" s="2">
         <v>20</v>
@@ -11040,22 +11229,22 @@
         <v>20</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>232</v>
+        <v>534</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>227</v>
+        <v>370</v>
       </c>
       <c r="AL73" t="s" s="2">
         <v>20</v>
@@ -11064,22 +11253,22 @@
         <v>20</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>20</v>
+        <v>535</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="74" hidden="true">
+    <row r="74">
       <c r="A74" t="s" s="2">
-        <v>568</v>
+        <v>536</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>568</v>
+        <v>536</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>569</v>
+        <v>20</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -11089,29 +11278,25 @@
         <v>80</v>
       </c>
       <c r="H74" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="I74" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="J74" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>133</v>
+        <v>270</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>570</v>
+        <v>537</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>211</v>
-      </c>
+        <v>538</v>
+      </c>
+      <c r="N74" s="2"/>
+      <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>20</v>
       </c>
@@ -11123,7 +11308,7 @@
         <v>20</v>
       </c>
       <c r="T74" t="s" s="2">
-        <v>20</v>
+        <v>539</v>
       </c>
       <c r="U74" t="s" s="2">
         <v>20</v>
@@ -11159,7 +11344,7 @@
         <v>20</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>572</v>
+        <v>540</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -11171,10 +11356,10 @@
         <v>20</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>131</v>
+        <v>541</v>
       </c>
       <c r="AL74" t="s" s="2">
         <v>20</v>
@@ -11183,52 +11368,50 @@
         <v>20</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>20</v>
+        <v>542</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="75" hidden="true">
+    <row r="75">
       <c r="A75" t="s" s="2">
-        <v>573</v>
+        <v>543</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>573</v>
+        <v>543</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>20</v>
+        <v>544</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H75" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="I75" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>244</v>
+        <v>270</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>574</v>
+        <v>545</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>575</v>
+        <v>546</v>
       </c>
       <c r="N75" s="2"/>
-      <c r="O75" t="s" s="2">
-        <v>576</v>
-      </c>
+      <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>20</v>
       </c>
@@ -11240,7 +11423,7 @@
         <v>20</v>
       </c>
       <c r="T75" t="s" s="2">
-        <v>20</v>
+        <v>547</v>
       </c>
       <c r="U75" t="s" s="2">
         <v>20</v>
@@ -11252,13 +11435,13 @@
         <v>20</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>249</v>
+        <v>20</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>577</v>
+        <v>20</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>578</v>
+        <v>20</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>20</v>
@@ -11276,13 +11459,13 @@
         <v>20</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>573</v>
+        <v>548</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>20</v>
@@ -11291,16 +11474,16 @@
         <v>100</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>579</v>
+        <v>549</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>227</v>
+        <v>20</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>580</v>
+        <v>550</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>20</v>
@@ -11308,14 +11491,14 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>581</v>
+        <v>551</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>581</v>
+        <v>551</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>20</v>
+        <v>552</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
@@ -11331,21 +11514,21 @@
         <v>20</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>582</v>
+        <v>270</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>583</v>
+        <v>553</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>584</v>
-      </c>
-      <c r="N76" s="2"/>
-      <c r="O76" t="s" s="2">
-        <v>585</v>
-      </c>
+        <v>554</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>20</v>
       </c>
@@ -11357,7 +11540,7 @@
         <v>20</v>
       </c>
       <c r="T76" t="s" s="2">
-        <v>20</v>
+        <v>556</v>
       </c>
       <c r="U76" t="s" s="2">
         <v>20</v>
@@ -11393,7 +11576,7 @@
         <v>20</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>581</v>
+        <v>557</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
@@ -11408,63 +11591,59 @@
         <v>100</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>302</v>
+        <v>558</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>227</v>
+        <v>20</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>586</v>
+        <v>559</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="77" hidden="true">
+    <row r="77">
       <c r="A77" t="s" s="2">
-        <v>587</v>
+        <v>560</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>587</v>
+        <v>560</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>20</v>
+        <v>561</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H77" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="I77" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>588</v>
+        <v>270</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>589</v>
+        <v>562</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="O77" t="s" s="2">
-        <v>366</v>
-      </c>
+        <v>563</v>
+      </c>
+      <c r="N77" s="2"/>
+      <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>20</v>
       </c>
@@ -11476,7 +11655,7 @@
         <v>20</v>
       </c>
       <c r="T77" t="s" s="2">
-        <v>20</v>
+        <v>564</v>
       </c>
       <c r="U77" t="s" s="2">
         <v>20</v>
@@ -11488,13 +11667,13 @@
         <v>20</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>20</v>
+        <v>296</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>20</v>
+        <v>565</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>20</v>
+        <v>566</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>20</v>
@@ -11512,13 +11691,13 @@
         <v>20</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>587</v>
+        <v>567</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>20</v>
@@ -11527,31 +11706,31 @@
         <v>100</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>367</v>
+        <v>568</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>227</v>
+        <v>20</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>592</v>
+        <v>569</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="78" hidden="true">
+    <row r="78">
       <c r="A78" t="s" s="2">
-        <v>593</v>
+        <v>570</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>593</v>
+        <v>570</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>20</v>
+        <v>571</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
@@ -11561,27 +11740,25 @@
         <v>88</v>
       </c>
       <c r="H78" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="I78" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>594</v>
+        <v>270</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>595</v>
+        <v>572</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>596</v>
+        <v>573</v>
       </c>
       <c r="N78" s="2"/>
-      <c r="O78" t="s" s="2">
-        <v>597</v>
-      </c>
+      <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>20</v>
       </c>
@@ -11593,7 +11770,7 @@
         <v>20</v>
       </c>
       <c r="T78" t="s" s="2">
-        <v>20</v>
+        <v>574</v>
       </c>
       <c r="U78" t="s" s="2">
         <v>20</v>
@@ -11629,7 +11806,7 @@
         <v>20</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>593</v>
+        <v>575</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
@@ -11644,16 +11821,16 @@
         <v>100</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>439</v>
+        <v>576</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>227</v>
+        <v>20</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>598</v>
+        <v>577</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>20</v>
@@ -11661,10 +11838,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>599</v>
+        <v>578</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>599</v>
+        <v>578</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11684,21 +11861,21 @@
         <v>20</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>108</v>
+        <v>270</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>408</v>
+        <v>579</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>600</v>
-      </c>
-      <c r="N79" s="2"/>
-      <c r="O79" t="s" s="2">
-        <v>601</v>
-      </c>
+        <v>580</v>
+      </c>
+      <c r="N79" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>20</v>
       </c>
@@ -11722,13 +11899,13 @@
         <v>20</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>238</v>
+        <v>20</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>602</v>
+        <v>20</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>603</v>
+        <v>20</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>20</v>
@@ -11746,7 +11923,7 @@
         <v>20</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>599</v>
+        <v>582</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
@@ -11761,16 +11938,16 @@
         <v>100</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>164</v>
+        <v>583</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>227</v>
+        <v>20</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>604</v>
+        <v>584</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>20</v>
@@ -11778,10 +11955,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>605</v>
+        <v>585</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>605</v>
+        <v>585</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11801,20 +11978,20 @@
         <v>20</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>279</v>
+        <v>319</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>606</v>
+        <v>586</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>607</v>
+        <v>587</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" t="s" s="2">
-        <v>608</v>
+        <v>588</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>20</v>
@@ -11827,7 +12004,7 @@
         <v>20</v>
       </c>
       <c r="T80" t="s" s="2">
-        <v>20</v>
+        <v>589</v>
       </c>
       <c r="U80" t="s" s="2">
         <v>20</v>
@@ -11863,7 +12040,7 @@
         <v>20</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>605</v>
+        <v>590</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>79</v>
@@ -11872,22 +12049,22 @@
         <v>88</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>609</v>
+        <v>20</v>
       </c>
       <c r="AJ80" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>610</v>
+        <v>406</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>227</v>
+        <v>20</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>611</v>
+        <v>591</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>20</v>
@@ -11895,10 +12072,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>612</v>
+        <v>592</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>612</v>
+        <v>592</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11921,16 +12098,18 @@
         <v>20</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>272</v>
+        <v>593</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>613</v>
+        <v>594</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>614</v>
+        <v>595</v>
       </c>
       <c r="N81" s="2"/>
-      <c r="O81" s="2"/>
+      <c r="O81" t="s" s="2">
+        <v>596</v>
+      </c>
       <c r="P81" t="s" s="2">
         <v>20</v>
       </c>
@@ -11954,13 +12133,13 @@
         <v>20</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>20</v>
+        <v>296</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>20</v>
+        <v>597</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>20</v>
+        <v>598</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>20</v>
@@ -11978,7 +12157,7 @@
         <v>20</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>612</v>
+        <v>592</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>79</v>
@@ -11993,16 +12172,16 @@
         <v>100</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>615</v>
+        <v>599</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>227</v>
+        <v>600</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>20</v>
+        <v>601</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>20</v>
@@ -12010,10 +12189,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>616</v>
+        <v>602</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>616</v>
+        <v>602</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12024,7 +12203,7 @@
         <v>79</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>20</v>
@@ -12036,19 +12215,19 @@
         <v>20</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>559</v>
+        <v>603</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>617</v>
+        <v>604</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>618</v>
+        <v>605</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>619</v>
+        <v>606</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>620</v>
+        <v>607</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>20</v>
@@ -12097,13 +12276,13 @@
         <v>20</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>616</v>
+        <v>602</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>20</v>
@@ -12112,16 +12291,16 @@
         <v>100</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>621</v>
+        <v>608</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>622</v>
+        <v>274</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>20</v>
+        <v>609</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>20</v>
@@ -12129,10 +12308,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>623</v>
+        <v>610</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>623</v>
+        <v>610</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12143,7 +12322,7 @@
         <v>79</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>20</v>
@@ -12155,16 +12334,20 @@
         <v>20</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>223</v>
+        <v>611</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>224</v>
+        <v>612</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="N83" s="2"/>
-      <c r="O83" s="2"/>
+        <v>613</v>
+      </c>
+      <c r="N83" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="O83" t="s" s="2">
+        <v>615</v>
+      </c>
       <c r="P83" t="s" s="2">
         <v>20</v>
       </c>
@@ -12212,31 +12395,31 @@
         <v>20</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>226</v>
+        <v>610</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>227</v>
+        <v>616</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>20</v>
+        <v>274</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>20</v>
+        <v>617</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>20</v>
@@ -12244,14 +12427,14 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>624</v>
+        <v>618</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>624</v>
+        <v>618</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>207</v>
+        <v>20</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
@@ -12270,18 +12453,20 @@
         <v>20</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>133</v>
+        <v>619</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>229</v>
+        <v>620</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>230</v>
+        <v>621</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="O84" s="2"/>
+        <v>622</v>
+      </c>
+      <c r="O84" t="s" s="2">
+        <v>623</v>
+      </c>
       <c r="P84" t="s" s="2">
         <v>20</v>
       </c>
@@ -12329,7 +12514,7 @@
         <v>20</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>232</v>
+        <v>618</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>79</v>
@@ -12341,13 +12526,13 @@
         <v>20</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>139</v>
+        <v>624</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>227</v>
+        <v>625</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>20</v>
+        <v>274</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>20</v>
@@ -12361,46 +12546,42 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>569</v>
+        <v>20</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I85" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>133</v>
+        <v>270</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>570</v>
+        <v>271</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="O85" t="s" s="2">
-        <v>211</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="N85" s="2"/>
+      <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>20</v>
       </c>
@@ -12448,22 +12629,22 @@
         <v>20</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>572</v>
+        <v>273</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>139</v>
+        <v>20</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>131</v>
+        <v>274</v>
       </c>
       <c r="AL85" t="s" s="2">
         <v>20</v>
@@ -12478,26 +12659,26 @@
         <v>20</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>20</v>
+        <v>254</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H86" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="I86" t="s" s="2">
         <v>20</v>
@@ -12506,20 +12687,18 @@
         <v>20</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>533</v>
+        <v>133</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>627</v>
+        <v>276</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>628</v>
+        <v>277</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>629</v>
-      </c>
-      <c r="O86" t="s" s="2">
-        <v>630</v>
-      </c>
+        <v>257</v>
+      </c>
+      <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>20</v>
       </c>
@@ -12543,11 +12722,13 @@
         <v>20</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="Y86" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="Y86" t="s" s="2">
+        <v>20</v>
+      </c>
       <c r="Z86" t="s" s="2">
-        <v>631</v>
+        <v>20</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>20</v>
@@ -12565,31 +12746,31 @@
         <v>20</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>626</v>
+        <v>279</v>
       </c>
       <c r="AG86" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>632</v>
+        <v>274</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>633</v>
+        <v>20</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>634</v>
+        <v>20</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>20</v>
@@ -12597,45 +12778,45 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>635</v>
+        <v>628</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>635</v>
+        <v>628</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>20</v>
+        <v>629</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I87" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>287</v>
+        <v>133</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>636</v>
+        <v>630</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>637</v>
+        <v>631</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>638</v>
+        <v>257</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>639</v>
+        <v>258</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>20</v>
@@ -12684,31 +12865,31 @@
         <v>20</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>640</v>
+        <v>131</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>641</v>
+        <v>20</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>642</v>
+        <v>20</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>20</v>
@@ -12716,14 +12897,14 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>643</v>
+        <v>633</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>643</v>
+        <v>633</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>644</v>
+        <v>20</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
@@ -12742,18 +12923,18 @@
         <v>20</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>645</v>
+        <v>291</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>646</v>
+        <v>634</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>647</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>648</v>
-      </c>
-      <c r="O88" s="2"/>
+        <v>635</v>
+      </c>
+      <c r="N88" s="2"/>
+      <c r="O88" t="s" s="2">
+        <v>636</v>
+      </c>
       <c r="P88" t="s" s="2">
         <v>20</v>
       </c>
@@ -12777,13 +12958,13 @@
         <v>20</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>20</v>
+        <v>296</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>20</v>
+        <v>637</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>20</v>
+        <v>638</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>20</v>
@@ -12801,7 +12982,7 @@
         <v>20</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>643</v>
+        <v>633</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>79</v>
@@ -12816,16 +12997,16 @@
         <v>100</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>649</v>
+        <v>639</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>227</v>
+        <v>274</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>650</v>
+        <v>640</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>20</v>
@@ -12833,10 +13014,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>651</v>
+        <v>641</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>651</v>
+        <v>641</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12856,22 +13037,20 @@
         <v>20</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>652</v>
+        <v>642</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>653</v>
+        <v>643</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>654</v>
-      </c>
-      <c r="N89" t="s" s="2">
-        <v>655</v>
-      </c>
+        <v>644</v>
+      </c>
+      <c r="N89" s="2"/>
       <c r="O89" t="s" s="2">
-        <v>656</v>
+        <v>645</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>20</v>
@@ -12920,7 +13099,7 @@
         <v>20</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>651</v>
+        <v>641</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>79</v>
@@ -12935,16 +13114,16 @@
         <v>100</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>610</v>
+        <v>349</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>657</v>
+        <v>274</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>20</v>
+        <v>646</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>20</v>
@@ -12952,10 +13131,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>658</v>
+        <v>647</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>658</v>
+        <v>647</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12972,25 +13151,25 @@
         <v>20</v>
       </c>
       <c r="I90" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>559</v>
+        <v>648</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>659</v>
+        <v>649</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>660</v>
+        <v>650</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>661</v>
+        <v>651</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>662</v>
+        <v>413</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>20</v>
@@ -13039,7 +13218,7 @@
         <v>20</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>658</v>
+        <v>647</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>79</v>
@@ -13054,16 +13233,16 @@
         <v>100</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>663</v>
+        <v>414</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>227</v>
+        <v>274</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>20</v>
+        <v>652</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>20</v>
@@ -13071,10 +13250,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>664</v>
+        <v>653</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>664</v>
+        <v>653</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13097,16 +13276,18 @@
         <v>20</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>223</v>
+        <v>654</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>224</v>
+        <v>655</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>225</v>
+        <v>656</v>
       </c>
       <c r="N91" s="2"/>
-      <c r="O91" s="2"/>
+      <c r="O91" t="s" s="2">
+        <v>657</v>
+      </c>
       <c r="P91" t="s" s="2">
         <v>20</v>
       </c>
@@ -13154,7 +13335,7 @@
         <v>20</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>226</v>
+        <v>653</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>79</v>
@@ -13166,19 +13347,19 @@
         <v>20</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>227</v>
+        <v>499</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>20</v>
+        <v>274</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>20</v>
+        <v>658</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>20</v>
@@ -13186,21 +13367,21 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>665</v>
+        <v>659</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>665</v>
+        <v>659</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>207</v>
+        <v>20</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>20</v>
@@ -13212,18 +13393,18 @@
         <v>20</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>133</v>
+        <v>108</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>229</v>
+        <v>455</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="O92" s="2"/>
+        <v>660</v>
+      </c>
+      <c r="N92" s="2"/>
+      <c r="O92" t="s" s="2">
+        <v>661</v>
+      </c>
       <c r="P92" t="s" s="2">
         <v>20</v>
       </c>
@@ -13247,13 +13428,13 @@
         <v>20</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>20</v>
+        <v>285</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>20</v>
+        <v>662</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>20</v>
+        <v>663</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>20</v>
@@ -13271,31 +13452,31 @@
         <v>20</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>232</v>
+        <v>659</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>227</v>
+        <v>164</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>20</v>
+        <v>274</v>
       </c>
       <c r="AM92" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>20</v>
+        <v>664</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>20</v>
@@ -13303,45 +13484,43 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>569</v>
+        <v>20</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I93" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="J93" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>133</v>
+        <v>326</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>570</v>
+        <v>666</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>210</v>
-      </c>
+        <v>667</v>
+      </c>
+      <c r="N93" s="2"/>
       <c r="O93" t="s" s="2">
-        <v>211</v>
+        <v>668</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>20</v>
@@ -13390,31 +13569,31 @@
         <v>20</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>572</v>
+        <v>665</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI93" t="s" s="2">
-        <v>20</v>
+        <v>669</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>131</v>
+        <v>670</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>20</v>
+        <v>274</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>20</v>
+        <v>671</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>20</v>
@@ -13422,10 +13601,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>667</v>
+        <v>672</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>667</v>
+        <v>672</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13433,7 +13612,7 @@
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G94" t="s" s="2">
         <v>88</v>
@@ -13445,20 +13624,18 @@
         <v>20</v>
       </c>
       <c r="J94" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>668</v>
+        <v>319</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>670</v>
-      </c>
-      <c r="N94" t="s" s="2">
-        <v>671</v>
-      </c>
+        <v>674</v>
+      </c>
+      <c r="N94" s="2"/>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
         <v>20</v>
@@ -13507,10 +13684,10 @@
         <v>20</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>667</v>
+        <v>672</v>
       </c>
       <c r="AG94" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AH94" t="s" s="2">
         <v>88</v>
@@ -13522,16 +13699,16 @@
         <v>100</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>218</v>
+        <v>675</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>227</v>
+        <v>274</v>
       </c>
       <c r="AM94" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>672</v>
+        <v>20</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>20</v>
@@ -13539,10 +13716,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13550,10 +13727,10 @@
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>20</v>
@@ -13562,19 +13739,23 @@
         <v>20</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>108</v>
+        <v>619</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>675</v>
-      </c>
-      <c r="N95" s="2"/>
-      <c r="O95" s="2"/>
+        <v>678</v>
+      </c>
+      <c r="N95" t="s" s="2">
+        <v>679</v>
+      </c>
+      <c r="O95" t="s" s="2">
+        <v>680</v>
+      </c>
       <c r="P95" t="s" s="2">
         <v>20</v>
       </c>
@@ -13598,37 +13779,37 @@
         <v>20</v>
       </c>
       <c r="X95" t="s" s="2">
-        <v>238</v>
+        <v>20</v>
       </c>
       <c r="Y95" t="s" s="2">
-        <v>675</v>
+        <v>20</v>
       </c>
       <c r="Z95" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA95" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB95" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC95" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD95" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE95" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF95" t="s" s="2">
         <v>676</v>
       </c>
-      <c r="AA95" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB95" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC95" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD95" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE95" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF95" t="s" s="2">
-        <v>673</v>
-      </c>
       <c r="AG95" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI95" t="s" s="2">
         <v>20</v>
@@ -13637,10 +13818,10 @@
         <v>100</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>227</v>
+        <v>682</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>20</v>
@@ -13649,11 +13830,1536 @@
         <v>20</v>
       </c>
       <c r="AO95" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="96" hidden="true">
+      <c r="A96" t="s" s="2">
+        <v>683</v>
+      </c>
+      <c r="B96" t="s" s="2">
+        <v>683</v>
+      </c>
+      <c r="C96" s="2"/>
+      <c r="D96" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E96" s="2"/>
+      <c r="F96" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G96" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H96" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I96" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J96" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K96" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="L96" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="M96" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="N96" s="2"/>
+      <c r="O96" s="2"/>
+      <c r="P96" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q96" s="2"/>
+      <c r="R96" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S96" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T96" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U96" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V96" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W96" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X96" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y96" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z96" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA96" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB96" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC96" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD96" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE96" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF96" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="AG96" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH96" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI96" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ96" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK96" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="AL96" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM96" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN96" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO96" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="97" hidden="true">
+      <c r="A97" t="s" s="2">
+        <v>684</v>
+      </c>
+      <c r="B97" t="s" s="2">
+        <v>684</v>
+      </c>
+      <c r="C97" s="2"/>
+      <c r="D97" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="E97" s="2"/>
+      <c r="F97" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H97" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I97" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J97" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K97" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L97" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="M97" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="N97" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="O97" s="2"/>
+      <c r="P97" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q97" s="2"/>
+      <c r="R97" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S97" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T97" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U97" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V97" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W97" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X97" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y97" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z97" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA97" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB97" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC97" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD97" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE97" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF97" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="AG97" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI97" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ97" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AK97" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="AL97" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM97" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN97" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO97" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="98" hidden="true">
+      <c r="A98" t="s" s="2">
+        <v>685</v>
+      </c>
+      <c r="B98" t="s" s="2">
+        <v>685</v>
+      </c>
+      <c r="C98" s="2"/>
+      <c r="D98" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="E98" s="2"/>
+      <c r="F98" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H98" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I98" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="J98" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K98" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L98" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="M98" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="N98" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="O98" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="P98" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q98" s="2"/>
+      <c r="R98" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S98" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T98" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U98" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V98" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W98" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X98" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y98" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z98" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA98" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB98" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC98" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD98" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE98" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF98" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="AG98" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI98" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ98" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AK98" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="AL98" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM98" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN98" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO98" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s" s="2">
+        <v>686</v>
+      </c>
+      <c r="B99" t="s" s="2">
+        <v>686</v>
+      </c>
+      <c r="C99" s="2"/>
+      <c r="D99" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E99" s="2"/>
+      <c r="F99" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G99" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H99" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="I99" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J99" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K99" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="L99" t="s" s="2">
+        <v>687</v>
+      </c>
+      <c r="M99" t="s" s="2">
+        <v>688</v>
+      </c>
+      <c r="N99" t="s" s="2">
+        <v>689</v>
+      </c>
+      <c r="O99" t="s" s="2">
+        <v>690</v>
+      </c>
+      <c r="P99" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q99" s="2"/>
+      <c r="R99" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S99" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T99" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U99" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V99" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W99" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X99" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="Y99" s="2"/>
+      <c r="Z99" t="s" s="2">
+        <v>691</v>
+      </c>
+      <c r="AA99" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB99" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC99" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD99" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE99" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF99" t="s" s="2">
+        <v>686</v>
+      </c>
+      <c r="AG99" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH99" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI99" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ99" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK99" t="s" s="2">
+        <v>692</v>
+      </c>
+      <c r="AL99" t="s" s="2">
+        <v>693</v>
+      </c>
+      <c r="AM99" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN99" t="s" s="2">
+        <v>694</v>
+      </c>
+      <c r="AO99" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="100" hidden="true">
+      <c r="A100" t="s" s="2">
+        <v>695</v>
+      </c>
+      <c r="B100" t="s" s="2">
+        <v>695</v>
+      </c>
+      <c r="C100" s="2"/>
+      <c r="D100" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E100" s="2"/>
+      <c r="F100" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G100" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H100" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I100" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J100" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K100" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="L100" t="s" s="2">
+        <v>696</v>
+      </c>
+      <c r="M100" t="s" s="2">
+        <v>697</v>
+      </c>
+      <c r="N100" t="s" s="2">
+        <v>698</v>
+      </c>
+      <c r="O100" t="s" s="2">
+        <v>699</v>
+      </c>
+      <c r="P100" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q100" s="2"/>
+      <c r="R100" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S100" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T100" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U100" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V100" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W100" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X100" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y100" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z100" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA100" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB100" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC100" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD100" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE100" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF100" t="s" s="2">
+        <v>695</v>
+      </c>
+      <c r="AG100" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH100" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI100" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ100" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK100" t="s" s="2">
+        <v>700</v>
+      </c>
+      <c r="AL100" t="s" s="2">
+        <v>701</v>
+      </c>
+      <c r="AM100" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN100" t="s" s="2">
+        <v>702</v>
+      </c>
+      <c r="AO100" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="101" hidden="true">
+      <c r="A101" t="s" s="2">
+        <v>703</v>
+      </c>
+      <c r="B101" t="s" s="2">
+        <v>703</v>
+      </c>
+      <c r="C101" s="2"/>
+      <c r="D101" t="s" s="2">
+        <v>704</v>
+      </c>
+      <c r="E101" s="2"/>
+      <c r="F101" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H101" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I101" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J101" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K101" t="s" s="2">
+        <v>705</v>
+      </c>
+      <c r="L101" t="s" s="2">
+        <v>706</v>
+      </c>
+      <c r="M101" t="s" s="2">
+        <v>707</v>
+      </c>
+      <c r="N101" t="s" s="2">
+        <v>708</v>
+      </c>
+      <c r="O101" s="2"/>
+      <c r="P101" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q101" s="2"/>
+      <c r="R101" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S101" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T101" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U101" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V101" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W101" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X101" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y101" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z101" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA101" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB101" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC101" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD101" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE101" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF101" t="s" s="2">
+        <v>703</v>
+      </c>
+      <c r="AG101" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI101" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ101" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK101" t="s" s="2">
+        <v>709</v>
+      </c>
+      <c r="AL101" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="AM101" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN101" t="s" s="2">
+        <v>710</v>
+      </c>
+      <c r="AO101" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="102" hidden="true">
+      <c r="A102" t="s" s="2">
+        <v>711</v>
+      </c>
+      <c r="B102" t="s" s="2">
+        <v>711</v>
+      </c>
+      <c r="C102" s="2"/>
+      <c r="D102" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E102" s="2"/>
+      <c r="F102" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G102" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H102" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I102" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J102" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K102" t="s" s="2">
+        <v>712</v>
+      </c>
+      <c r="L102" t="s" s="2">
+        <v>713</v>
+      </c>
+      <c r="M102" t="s" s="2">
+        <v>714</v>
+      </c>
+      <c r="N102" t="s" s="2">
+        <v>715</v>
+      </c>
+      <c r="O102" t="s" s="2">
+        <v>716</v>
+      </c>
+      <c r="P102" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q102" s="2"/>
+      <c r="R102" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S102" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T102" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U102" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V102" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W102" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X102" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y102" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z102" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA102" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB102" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC102" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD102" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE102" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF102" t="s" s="2">
+        <v>711</v>
+      </c>
+      <c r="AG102" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH102" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI102" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ102" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK102" t="s" s="2">
+        <v>670</v>
+      </c>
+      <c r="AL102" t="s" s="2">
+        <v>717</v>
+      </c>
+      <c r="AM102" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN102" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO102" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="103" hidden="true">
+      <c r="A103" t="s" s="2">
+        <v>718</v>
+      </c>
+      <c r="B103" t="s" s="2">
+        <v>718</v>
+      </c>
+      <c r="C103" s="2"/>
+      <c r="D103" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E103" s="2"/>
+      <c r="F103" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H103" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I103" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="J103" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K103" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="L103" t="s" s="2">
+        <v>719</v>
+      </c>
+      <c r="M103" t="s" s="2">
+        <v>720</v>
+      </c>
+      <c r="N103" t="s" s="2">
+        <v>721</v>
+      </c>
+      <c r="O103" t="s" s="2">
+        <v>722</v>
+      </c>
+      <c r="P103" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q103" s="2"/>
+      <c r="R103" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S103" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T103" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U103" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V103" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W103" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X103" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y103" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z103" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA103" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB103" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC103" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD103" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE103" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF103" t="s" s="2">
+        <v>718</v>
+      </c>
+      <c r="AG103" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI103" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ103" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK103" t="s" s="2">
+        <v>723</v>
+      </c>
+      <c r="AL103" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="AM103" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN103" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO103" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="104" hidden="true">
+      <c r="A104" t="s" s="2">
+        <v>724</v>
+      </c>
+      <c r="B104" t="s" s="2">
+        <v>724</v>
+      </c>
+      <c r="C104" s="2"/>
+      <c r="D104" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E104" s="2"/>
+      <c r="F104" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G104" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H104" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I104" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J104" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K104" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="L104" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="M104" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="N104" s="2"/>
+      <c r="O104" s="2"/>
+      <c r="P104" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q104" s="2"/>
+      <c r="R104" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S104" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T104" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U104" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V104" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W104" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X104" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y104" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z104" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA104" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB104" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC104" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD104" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE104" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF104" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="AG104" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH104" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI104" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ104" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK104" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="AL104" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM104" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN104" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO104" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="105" hidden="true">
+      <c r="A105" t="s" s="2">
+        <v>725</v>
+      </c>
+      <c r="B105" t="s" s="2">
+        <v>725</v>
+      </c>
+      <c r="C105" s="2"/>
+      <c r="D105" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="E105" s="2"/>
+      <c r="F105" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H105" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I105" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J105" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K105" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L105" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="M105" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="N105" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="O105" s="2"/>
+      <c r="P105" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q105" s="2"/>
+      <c r="R105" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S105" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T105" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U105" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V105" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W105" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X105" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y105" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z105" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA105" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB105" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC105" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD105" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE105" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF105" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="AG105" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI105" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ105" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AK105" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="AL105" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM105" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN105" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO105" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="106" hidden="true">
+      <c r="A106" t="s" s="2">
+        <v>726</v>
+      </c>
+      <c r="B106" t="s" s="2">
+        <v>726</v>
+      </c>
+      <c r="C106" s="2"/>
+      <c r="D106" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="E106" s="2"/>
+      <c r="F106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H106" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I106" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="J106" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K106" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L106" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="M106" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="N106" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="O106" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="P106" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q106" s="2"/>
+      <c r="R106" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S106" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T106" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U106" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V106" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W106" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X106" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y106" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z106" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA106" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB106" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC106" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD106" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE106" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF106" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="AG106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI106" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ106" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AK106" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="AL106" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM106" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN106" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO106" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="107" hidden="true">
+      <c r="A107" t="s" s="2">
+        <v>727</v>
+      </c>
+      <c r="B107" t="s" s="2">
+        <v>727</v>
+      </c>
+      <c r="C107" s="2"/>
+      <c r="D107" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E107" s="2"/>
+      <c r="F107" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G107" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H107" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I107" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J107" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K107" t="s" s="2">
+        <v>728</v>
+      </c>
+      <c r="L107" t="s" s="2">
+        <v>729</v>
+      </c>
+      <c r="M107" t="s" s="2">
+        <v>730</v>
+      </c>
+      <c r="N107" t="s" s="2">
+        <v>731</v>
+      </c>
+      <c r="O107" s="2"/>
+      <c r="P107" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q107" s="2"/>
+      <c r="R107" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S107" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T107" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U107" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V107" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W107" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X107" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y107" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z107" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA107" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB107" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC107" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD107" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE107" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF107" t="s" s="2">
+        <v>727</v>
+      </c>
+      <c r="AG107" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH107" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI107" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ107" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK107" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="AL107" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="AM107" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN107" t="s" s="2">
+        <v>732</v>
+      </c>
+      <c r="AO107" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="108" hidden="true">
+      <c r="A108" t="s" s="2">
+        <v>733</v>
+      </c>
+      <c r="B108" t="s" s="2">
+        <v>733</v>
+      </c>
+      <c r="C108" s="2"/>
+      <c r="D108" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E108" s="2"/>
+      <c r="F108" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G108" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H108" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I108" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J108" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K108" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="L108" t="s" s="2">
+        <v>734</v>
+      </c>
+      <c r="M108" t="s" s="2">
+        <v>735</v>
+      </c>
+      <c r="N108" s="2"/>
+      <c r="O108" s="2"/>
+      <c r="P108" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q108" s="2"/>
+      <c r="R108" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S108" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T108" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U108" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V108" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W108" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X108" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="Y108" t="s" s="2">
+        <v>735</v>
+      </c>
+      <c r="Z108" t="s" s="2">
+        <v>736</v>
+      </c>
+      <c r="AA108" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB108" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC108" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD108" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE108" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF108" t="s" s="2">
+        <v>733</v>
+      </c>
+      <c r="AG108" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH108" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI108" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ108" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK108" t="s" s="2">
+        <v>737</v>
+      </c>
+      <c r="AL108" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="AM108" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN108" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO108" t="s" s="2">
         <v>20</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO95">
+  <autoFilter ref="A1:AO108">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -13663,7 +15369,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI94">
+  <conditionalFormatting sqref="A2:AI107">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
